--- a/arquivos/frequencias/modelo-frequencia.xlsx
+++ b/arquivos/frequencias/modelo-frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dougl\Desktop\Eng\Work\RELATÓRIOS\prefeitura-docs\arquivos\frequencias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E0D2ACD-D046-48BB-937B-0C4DC0F3D170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0768AE-7AC9-40A5-80B3-B2317C494B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0D801A56-3C50-4F7C-A8C3-220900B298F7}"/>
   </bookViews>
@@ -111,7 +111,7 @@
     <t>Lotação: SECRETARIA DE URBANISMO, OBRAS E SERVIÇOS PÚBLICOS</t>
   </si>
   <si>
-    <t>SECRETARIA DE URBANIMSO</t>
+    <t>SECRETARIA DE URBANISMO</t>
   </si>
 </sst>
 </file>
@@ -317,9 +317,6 @@
   <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -327,170 +324,173 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -894,15 +894,15 @@
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
@@ -915,15 +915,15 @@
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
@@ -936,15 +936,15 @@
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
@@ -957,19 +957,19 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="57"/>
-      <c r="M5" s="61"/>
-      <c r="N5" s="61"/>
-      <c r="O5" s="61"/>
-      <c r="P5" s="61"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
@@ -978,21 +978,21 @@
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="59" t="s">
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="M6" s="61"/>
-      <c r="N6" s="61"/>
-      <c r="O6" s="61"/>
-      <c r="P6" s="61"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
@@ -1001,15 +1001,15 @@
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="59" t="s">
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M7" s="1"/>
@@ -1032,7 +1032,7 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
-      <c r="L8" s="60" t="s">
+      <c r="L8" s="10" t="s">
         <v>23</v>
       </c>
       <c r="M8" s="1"/>
@@ -1051,12 +1051,12 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="60"/>
+      <c r="J9" s="60"/>
+      <c r="K9" s="60"/>
+      <c r="L9" s="60"/>
+      <c r="M9" s="60"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
@@ -1090,16 +1090,16 @@
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
-      <c r="E11" s="56" t="s">
+      <c r="E11" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="56"/>
-      <c r="G11" s="56"/>
-      <c r="H11" s="56"/>
-      <c r="I11" s="56"/>
-      <c r="J11" s="56"/>
-      <c r="K11" s="56"/>
-      <c r="L11" s="56"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -1134,16 +1134,16 @@
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
-      <c r="E13" s="37" t="s">
+      <c r="E13" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="29"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="14"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31"/>
+      <c r="K13" s="31"/>
+      <c r="L13" s="32"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
@@ -1157,14 +1157,14 @@
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
-      <c r="K14" s="30"/>
-      <c r="L14" s="16"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="34"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
@@ -1178,16 +1178,16 @@
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
-      <c r="E15" s="31" t="s">
+      <c r="E15" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
-      <c r="K15" s="32"/>
-      <c r="L15" s="33"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="30"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
@@ -1201,18 +1201,18 @@
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
-      <c r="E16" s="36" t="s">
+      <c r="E16" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34" t="s">
+      <c r="F16" s="38"/>
+      <c r="G16" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="H16" s="34"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="34"/>
-      <c r="K16" s="34"/>
-      <c r="L16" s="35"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="38"/>
+      <c r="L16" s="39"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
@@ -1226,18 +1226,18 @@
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
-      <c r="E17" s="51" t="s">
+      <c r="E17" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="F17" s="41" t="s">
+      <c r="F17" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="41"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="41"/>
-      <c r="J17" s="41"/>
-      <c r="K17" s="41"/>
-      <c r="L17" s="42"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="17"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
@@ -1251,14 +1251,14 @@
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
-      <c r="E18" s="52"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="49"/>
-      <c r="J18" s="49"/>
-      <c r="K18" s="49"/>
-      <c r="L18" s="50"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="20"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
@@ -1272,18 +1272,18 @@
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
-      <c r="E19" s="46" t="s">
+      <c r="E19" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F19" s="47"/>
-      <c r="G19" s="47"/>
-      <c r="H19" s="58"/>
-      <c r="I19" s="48" t="s">
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="J19" s="39"/>
-      <c r="K19" s="39"/>
-      <c r="L19" s="40"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="23"/>
+      <c r="L19" s="24"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
@@ -1297,18 +1297,18 @@
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
-      <c r="E20" s="45" t="s">
+      <c r="E20" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="53" t="s">
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="J20" s="54"/>
-      <c r="K20" s="54"/>
-      <c r="L20" s="55"/>
+      <c r="J20" s="26"/>
+      <c r="K20" s="26"/>
+      <c r="L20" s="27"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
@@ -1338,27 +1338,27 @@
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="9" t="s">
+      <c r="G22" s="61"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="J22" s="10"/>
-      <c r="K22" s="13" t="s">
+      <c r="J22" s="57"/>
+      <c r="K22" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="L22" s="14"/>
+      <c r="L22" s="32"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
@@ -1367,27 +1367,27 @@
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="6" t="s">
+      <c r="E23" s="61"/>
+      <c r="F23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G23" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="H23" s="10"/>
-      <c r="I23" s="6" t="s">
+      <c r="H23" s="57"/>
+      <c r="I23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J23" s="6" t="s">
+      <c r="J23" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="K23" s="15"/>
-      <c r="L23" s="16"/>
+      <c r="K23" s="59"/>
+      <c r="L23" s="34"/>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
@@ -1396,21 +1396,21 @@
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
-      <c r="E24" s="7">
+      <c r="E24" s="4">
         <v>1</v>
       </c>
-      <c r="F24" s="8"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="12"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="42"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="42"/>
+      <c r="L24" s="43"/>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
@@ -1419,21 +1419,21 @@
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
-      <c r="E25" s="7">
+      <c r="E25" s="4">
         <v>2</v>
       </c>
-      <c r="F25" s="8"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="12"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="42"/>
+      <c r="L25" s="43"/>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
@@ -1442,21 +1442,21 @@
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
-      <c r="E26" s="7">
+      <c r="E26" s="4">
         <v>3</v>
       </c>
-      <c r="F26" s="8"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="12"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="42"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="42"/>
+      <c r="L26" s="43"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
@@ -1465,21 +1465,21 @@
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
-      <c r="E27" s="7">
+      <c r="E27" s="4">
         <v>4</v>
       </c>
-      <c r="F27" s="8"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="12"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="42"/>
+      <c r="L27" s="43"/>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
@@ -1488,21 +1488,21 @@
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
-      <c r="E28" s="7">
+      <c r="E28" s="4">
         <v>5</v>
       </c>
-      <c r="F28" s="8"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="11"/>
-      <c r="L28" s="12"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="42"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="42"/>
+      <c r="L28" s="43"/>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
@@ -1511,21 +1511,21 @@
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
-      <c r="E29" s="7">
+      <c r="E29" s="4">
         <v>6</v>
       </c>
-      <c r="F29" s="8"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="12"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="42"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="42"/>
+      <c r="L29" s="43"/>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
@@ -1534,21 +1534,21 @@
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
-      <c r="E30" s="7">
+      <c r="E30" s="4">
         <v>7</v>
       </c>
-      <c r="F30" s="8"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="11"/>
-      <c r="L30" s="12"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="42"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="42"/>
+      <c r="L30" s="43"/>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
@@ -1557,21 +1557,21 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
-      <c r="E31" s="7">
+      <c r="E31" s="4">
         <v>8</v>
       </c>
-      <c r="F31" s="8"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
-      <c r="K31" s="11"/>
-      <c r="L31" s="12"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="42"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="42"/>
+      <c r="L31" s="43"/>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
@@ -1580,21 +1580,21 @@
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="7">
+      <c r="E32" s="4">
         <v>9</v>
       </c>
-      <c r="F32" s="8"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="12"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="42"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="42"/>
+      <c r="L32" s="43"/>
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
@@ -1603,21 +1603,21 @@
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="7">
+      <c r="E33" s="4">
         <v>10</v>
       </c>
-      <c r="F33" s="8"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="8"/>
-      <c r="J33" s="8"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="12"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="42"/>
+      <c r="H33" s="43"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="42"/>
+      <c r="L33" s="43"/>
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
@@ -1626,21 +1626,21 @@
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
-      <c r="E34" s="7">
+      <c r="E34" s="4">
         <v>11</v>
       </c>
-      <c r="F34" s="8"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
-      <c r="K34" s="11"/>
-      <c r="L34" s="12"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="42"/>
+      <c r="H34" s="43"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="42"/>
+      <c r="L34" s="43"/>
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
@@ -1649,21 +1649,21 @@
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
-      <c r="E35" s="7">
+      <c r="E35" s="4">
         <v>12</v>
       </c>
-      <c r="F35" s="8"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="8"/>
-      <c r="J35" s="8"/>
-      <c r="K35" s="11"/>
-      <c r="L35" s="12"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="42"/>
+      <c r="H35" s="43"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="42"/>
+      <c r="L35" s="43"/>
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
@@ -1672,21 +1672,21 @@
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
-      <c r="E36" s="7">
+      <c r="E36" s="4">
         <v>13</v>
       </c>
-      <c r="F36" s="8"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="8"/>
-      <c r="J36" s="8"/>
-      <c r="K36" s="11"/>
-      <c r="L36" s="12"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="42"/>
+      <c r="H36" s="43"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="42"/>
+      <c r="L36" s="43"/>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
@@ -1695,21 +1695,21 @@
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="7">
+      <c r="E37" s="4">
         <v>14</v>
       </c>
-      <c r="F37" s="8"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="8"/>
-      <c r="J37" s="8"/>
-      <c r="K37" s="11"/>
-      <c r="L37" s="12"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="42"/>
+      <c r="H37" s="43"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="42"/>
+      <c r="L37" s="43"/>
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
@@ -1718,21 +1718,21 @@
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
-      <c r="E38" s="7">
+      <c r="E38" s="4">
         <v>15</v>
       </c>
-      <c r="F38" s="8"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="12"/>
-      <c r="I38" s="8"/>
-      <c r="J38" s="8"/>
-      <c r="K38" s="11"/>
-      <c r="L38" s="12"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="42"/>
+      <c r="H38" s="43"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="42"/>
+      <c r="L38" s="43"/>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
@@ -1741,21 +1741,21 @@
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
-      <c r="E39" s="7">
+      <c r="E39" s="4">
         <v>16</v>
       </c>
-      <c r="F39" s="8"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="8"/>
-      <c r="J39" s="8"/>
-      <c r="K39" s="11"/>
-      <c r="L39" s="12"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="42"/>
+      <c r="H39" s="43"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="42"/>
+      <c r="L39" s="43"/>
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
@@ -1764,21 +1764,21 @@
       <c r="R39" s="1"/>
       <c r="S39" s="1"/>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
-      <c r="E40" s="7">
+      <c r="E40" s="4">
         <v>17</v>
       </c>
-      <c r="F40" s="8"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="12"/>
-      <c r="I40" s="8"/>
-      <c r="J40" s="8"/>
-      <c r="K40" s="11"/>
-      <c r="L40" s="12"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="42"/>
+      <c r="H40" s="43"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="42"/>
+      <c r="L40" s="43"/>
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
@@ -1787,21 +1787,21 @@
       <c r="R40" s="1"/>
       <c r="S40" s="1"/>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
-      <c r="E41" s="7">
+      <c r="E41" s="4">
         <v>18</v>
       </c>
-      <c r="F41" s="8"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="12"/>
-      <c r="I41" s="8"/>
-      <c r="J41" s="8"/>
-      <c r="K41" s="11"/>
-      <c r="L41" s="12"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="42"/>
+      <c r="H41" s="43"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="42"/>
+      <c r="L41" s="43"/>
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
@@ -1810,21 +1810,21 @@
       <c r="R41" s="1"/>
       <c r="S41" s="1"/>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
-      <c r="E42" s="7">
+      <c r="E42" s="4">
         <v>19</v>
       </c>
-      <c r="F42" s="8"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="12"/>
-      <c r="I42" s="8"/>
-      <c r="J42" s="8"/>
-      <c r="K42" s="11"/>
-      <c r="L42" s="12"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="42"/>
+      <c r="H42" s="43"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="42"/>
+      <c r="L42" s="43"/>
       <c r="M42" s="1"/>
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
@@ -1833,21 +1833,21 @@
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
-      <c r="E43" s="7">
+      <c r="E43" s="4">
         <v>20</v>
       </c>
-      <c r="F43" s="8"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="12"/>
-      <c r="I43" s="8"/>
-      <c r="J43" s="8"/>
-      <c r="K43" s="11"/>
-      <c r="L43" s="12"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="42"/>
+      <c r="H43" s="43"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="42"/>
+      <c r="L43" s="43"/>
       <c r="M43" s="1"/>
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
@@ -1856,21 +1856,21 @@
       <c r="R43" s="1"/>
       <c r="S43" s="1"/>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
-      <c r="E44" s="7">
+      <c r="E44" s="4">
         <v>21</v>
       </c>
-      <c r="F44" s="8"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="12"/>
-      <c r="I44" s="8"/>
-      <c r="J44" s="8"/>
-      <c r="K44" s="11"/>
-      <c r="L44" s="12"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="42"/>
+      <c r="H44" s="43"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="42"/>
+      <c r="L44" s="43"/>
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
@@ -1879,21 +1879,21 @@
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
-      <c r="E45" s="7">
+      <c r="E45" s="4">
         <v>22</v>
       </c>
-      <c r="F45" s="8"/>
-      <c r="G45" s="11"/>
-      <c r="H45" s="12"/>
-      <c r="I45" s="8"/>
-      <c r="J45" s="8"/>
-      <c r="K45" s="11"/>
-      <c r="L45" s="12"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="42"/>
+      <c r="H45" s="43"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="42"/>
+      <c r="L45" s="43"/>
       <c r="M45" s="1"/>
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
@@ -1902,21 +1902,21 @@
       <c r="R45" s="1"/>
       <c r="S45" s="1"/>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
-      <c r="E46" s="7">
+      <c r="E46" s="4">
         <v>23</v>
       </c>
-      <c r="F46" s="8"/>
-      <c r="G46" s="11"/>
-      <c r="H46" s="12"/>
-      <c r="I46" s="8"/>
-      <c r="J46" s="8"/>
-      <c r="K46" s="11"/>
-      <c r="L46" s="12"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="42"/>
+      <c r="H46" s="43"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="42"/>
+      <c r="L46" s="43"/>
       <c r="M46" s="1"/>
       <c r="N46" s="1"/>
       <c r="O46" s="1"/>
@@ -1925,21 +1925,21 @@
       <c r="R46" s="1"/>
       <c r="S46" s="1"/>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
-      <c r="E47" s="7">
+      <c r="E47" s="4">
         <v>24</v>
       </c>
-      <c r="F47" s="8"/>
-      <c r="G47" s="11"/>
-      <c r="H47" s="12"/>
-      <c r="I47" s="8"/>
-      <c r="J47" s="8"/>
-      <c r="K47" s="11"/>
-      <c r="L47" s="12"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="42"/>
+      <c r="H47" s="43"/>
+      <c r="I47" s="5"/>
+      <c r="J47" s="5"/>
+      <c r="K47" s="42"/>
+      <c r="L47" s="43"/>
       <c r="M47" s="1"/>
       <c r="N47" s="1"/>
       <c r="O47" s="1"/>
@@ -1948,21 +1948,21 @@
       <c r="R47" s="1"/>
       <c r="S47" s="1"/>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
-      <c r="E48" s="7">
+      <c r="E48" s="4">
         <v>25</v>
       </c>
-      <c r="F48" s="8"/>
-      <c r="G48" s="11"/>
-      <c r="H48" s="12"/>
-      <c r="I48" s="8"/>
-      <c r="J48" s="8"/>
-      <c r="K48" s="11"/>
-      <c r="L48" s="12"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="42"/>
+      <c r="H48" s="43"/>
+      <c r="I48" s="5"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="42"/>
+      <c r="L48" s="43"/>
       <c r="M48" s="1"/>
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
@@ -1971,21 +1971,21 @@
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
-      <c r="E49" s="7">
+      <c r="E49" s="4">
         <v>26</v>
       </c>
-      <c r="F49" s="8"/>
-      <c r="G49" s="11"/>
-      <c r="H49" s="12"/>
-      <c r="I49" s="8"/>
-      <c r="J49" s="8"/>
-      <c r="K49" s="11"/>
-      <c r="L49" s="12"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="42"/>
+      <c r="H49" s="43"/>
+      <c r="I49" s="5"/>
+      <c r="J49" s="5"/>
+      <c r="K49" s="42"/>
+      <c r="L49" s="43"/>
       <c r="M49" s="1"/>
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
@@ -1994,21 +1994,21 @@
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
-      <c r="E50" s="7">
+      <c r="E50" s="4">
         <v>27</v>
       </c>
-      <c r="F50" s="8"/>
-      <c r="G50" s="11"/>
-      <c r="H50" s="12"/>
-      <c r="I50" s="8"/>
-      <c r="J50" s="8"/>
-      <c r="K50" s="11"/>
-      <c r="L50" s="12"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="42"/>
+      <c r="H50" s="43"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="42"/>
+      <c r="L50" s="43"/>
       <c r="M50" s="1"/>
       <c r="N50" s="1"/>
       <c r="O50" s="1"/>
@@ -2017,21 +2017,21 @@
       <c r="R50" s="1"/>
       <c r="S50" s="1"/>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
-      <c r="E51" s="7">
+      <c r="E51" s="4">
         <v>28</v>
       </c>
-      <c r="F51" s="8"/>
-      <c r="G51" s="11"/>
-      <c r="H51" s="12"/>
-      <c r="I51" s="8"/>
-      <c r="J51" s="8"/>
-      <c r="K51" s="11"/>
-      <c r="L51" s="12"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="42"/>
+      <c r="H51" s="43"/>
+      <c r="I51" s="5"/>
+      <c r="J51" s="5"/>
+      <c r="K51" s="42"/>
+      <c r="L51" s="43"/>
       <c r="M51" s="1"/>
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
@@ -2040,21 +2040,21 @@
       <c r="R51" s="1"/>
       <c r="S51" s="1"/>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="7">
+      <c r="E52" s="4">
         <v>29</v>
       </c>
-      <c r="F52" s="8"/>
-      <c r="G52" s="11"/>
-      <c r="H52" s="12"/>
-      <c r="I52" s="8"/>
-      <c r="J52" s="8"/>
-      <c r="K52" s="11"/>
-      <c r="L52" s="12"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="42"/>
+      <c r="H52" s="43"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="5"/>
+      <c r="K52" s="42"/>
+      <c r="L52" s="43"/>
       <c r="M52" s="1"/>
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
@@ -2063,21 +2063,21 @@
       <c r="R52" s="1"/>
       <c r="S52" s="1"/>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
-      <c r="E53" s="7">
+      <c r="E53" s="4">
         <v>30</v>
       </c>
-      <c r="F53" s="8"/>
-      <c r="G53" s="11"/>
-      <c r="H53" s="12"/>
-      <c r="I53" s="8"/>
-      <c r="J53" s="8"/>
-      <c r="K53" s="11"/>
-      <c r="L53" s="12"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="42"/>
+      <c r="H53" s="43"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="5"/>
+      <c r="K53" s="42"/>
+      <c r="L53" s="43"/>
       <c r="M53" s="1"/>
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
@@ -2086,21 +2086,21 @@
       <c r="R53" s="1"/>
       <c r="S53" s="1"/>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
-      <c r="E54" s="7">
+      <c r="E54" s="4">
         <v>31</v>
       </c>
-      <c r="F54" s="8"/>
-      <c r="G54" s="11"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="8"/>
-      <c r="J54" s="8"/>
-      <c r="K54" s="11"/>
-      <c r="L54" s="12"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="42"/>
+      <c r="H54" s="43"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="5"/>
+      <c r="K54" s="42"/>
+      <c r="L54" s="43"/>
       <c r="M54" s="1"/>
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
@@ -2135,14 +2135,14 @@
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
-      <c r="E56" s="19"/>
-      <c r="F56" s="20"/>
-      <c r="G56" s="21"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="5"/>
-      <c r="J56" s="5"/>
-      <c r="K56" s="5"/>
-      <c r="L56" s="5"/>
+      <c r="E56" s="47"/>
+      <c r="F56" s="48"/>
+      <c r="G56" s="49"/>
+      <c r="H56" s="43"/>
+      <c r="I56" s="44"/>
+      <c r="J56" s="44"/>
+      <c r="K56" s="44"/>
+      <c r="L56" s="44"/>
       <c r="M56" s="1"/>
       <c r="N56" s="1"/>
       <c r="O56" s="1"/>
@@ -2156,16 +2156,16 @@
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
-      <c r="E57" s="27" t="s">
+      <c r="E57" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="F57" s="26"/>
-      <c r="G57" s="28"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="5"/>
-      <c r="J57" s="5"/>
-      <c r="K57" s="5"/>
-      <c r="L57" s="5"/>
+      <c r="F57" s="51"/>
+      <c r="G57" s="52"/>
+      <c r="H57" s="43"/>
+      <c r="I57" s="44"/>
+      <c r="J57" s="44"/>
+      <c r="K57" s="44"/>
+      <c r="L57" s="44"/>
       <c r="M57" s="1"/>
       <c r="N57" s="1"/>
       <c r="O57" s="1"/>
@@ -2179,14 +2179,14 @@
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
-      <c r="E58" s="22"/>
-      <c r="F58" s="23"/>
-      <c r="G58" s="24"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="5"/>
-      <c r="J58" s="5"/>
-      <c r="K58" s="5"/>
-      <c r="L58" s="5"/>
+      <c r="E58" s="53"/>
+      <c r="F58" s="54"/>
+      <c r="G58" s="55"/>
+      <c r="H58" s="43"/>
+      <c r="I58" s="44"/>
+      <c r="J58" s="44"/>
+      <c r="K58" s="44"/>
+      <c r="L58" s="44"/>
       <c r="M58" s="1"/>
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
@@ -2200,18 +2200,18 @@
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
-      <c r="E59" s="25" t="s">
+      <c r="E59" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="F59" s="25"/>
-      <c r="G59" s="25"/>
-      <c r="H59" s="17" t="s">
+      <c r="F59" s="45"/>
+      <c r="G59" s="45"/>
+      <c r="H59" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="I59" s="17"/>
-      <c r="J59" s="17"/>
-      <c r="K59" s="17"/>
-      <c r="L59" s="18" t="s">
+      <c r="I59" s="46"/>
+      <c r="J59" s="46"/>
+      <c r="K59" s="46"/>
+      <c r="L59" s="6" t="s">
         <v>10</v>
       </c>
       <c r="M59" s="1"/>
@@ -3224,6 +3224,80 @@
     </row>
   </sheetData>
   <mergeCells count="86">
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G52:H52"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="K22:L23"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="K36:L36"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="K41:L41"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="K45:L45"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="K48:L48"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="K50:L50"/>
+    <mergeCell ref="K51:L51"/>
+    <mergeCell ref="K52:L52"/>
+    <mergeCell ref="K53:L53"/>
+    <mergeCell ref="K54:L54"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="H56:K58"/>
+    <mergeCell ref="L56:L58"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="H59:K59"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="E57:G58"/>
     <mergeCell ref="E11:L11"/>
     <mergeCell ref="E19:H19"/>
     <mergeCell ref="F17:L18"/>
@@ -3236,83 +3310,9 @@
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="G16:L16"/>
     <mergeCell ref="E17:E18"/>
-    <mergeCell ref="G54:H54"/>
-    <mergeCell ref="H56:K58"/>
-    <mergeCell ref="L56:L58"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="H59:K59"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="E57:G58"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="G47:H47"/>
-    <mergeCell ref="G48:H48"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="K50:L50"/>
-    <mergeCell ref="K51:L51"/>
-    <mergeCell ref="K52:L52"/>
-    <mergeCell ref="K53:L53"/>
-    <mergeCell ref="K54:L54"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="K44:L44"/>
-    <mergeCell ref="K45:L45"/>
-    <mergeCell ref="K46:L46"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="K48:L48"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="K41:L41"/>
-    <mergeCell ref="K42:L42"/>
-    <mergeCell ref="K43:L43"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="K22:L23"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="G52:H52"/>
-    <mergeCell ref="G53:H53"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="G45:H45"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="I22:J22"/>
   </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" scale="59" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="76" orientation="portrait" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="61" max="16383" man="1"/>
   </rowBreaks>
